--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/20-resumo-do-mes.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/20-resumo-do-mes.xlsx
@@ -638,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -799,17 +799,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -910,23 +922,23 @@
       </c>
       <c r="B5" s="9" t="str">
         <f>IF(Q5="","",IF(Indicadores!B5="R$","R$ ","")&amp;FIXED(Q5,N5)&amp;IF(Indicadores!B5="%","%",IF(OR(Indicadores!B5="R$",Indicadores!B5="",Indicadores!B5="un"),""," "&amp;Indicadores!B5)))</f>
-        <v>R$ 26,900</v>
+        <v>R$ 26.900</v>
       </c>
       <c r="C5" s="9" t="str">
         <f>IF(R5="","",IF(Indicadores!B5="R$","R$ ","")&amp;FIXED(R5,N5)&amp;IF(Indicadores!B5="%","%",IF(OR(Indicadores!B5="R$",Indicadores!B5="",Indicadores!B5="un"),""," "&amp;Indicadores!B5)))</f>
-        <v>R$ 29,460</v>
+        <v>R$ 29.460</v>
       </c>
       <c r="D5" s="9" t="str">
         <f>IF(T5="","",IF(T5&gt;=0,"+","")&amp;IF(Indicadores!B5="%",FIXED(T5,1)&amp;" p.p.",FIXED(T5*100,1)&amp;"%"))</f>
-        <v>-8.7%</v>
+        <v>-8,7%</v>
       </c>
       <c r="E5" s="9" t="str">
         <f>IF(S5="","",IF(Indicadores!B5="R$","R$ ","")&amp;FIXED(S5,N5)&amp;IF(Indicadores!B5="%","%",IF(OR(Indicadores!B5="R$",Indicadores!B5="",Indicadores!B5="un"),""," "&amp;Indicadores!B5)))</f>
-        <v>R$ 26,000</v>
+        <v>R$ 26.000</v>
       </c>
       <c r="F5" s="9" t="str">
         <f>IF(U5="","",IF(U5&gt;=0,"+","")&amp;IF(Indicadores!B5="%",FIXED(U5,1)&amp;" p.p.",FIXED(U5*100,1)&amp;"%"))</f>
-        <v>+3.5%</v>
+        <v>+3,5%</v>
       </c>
       <c r="G5" s="9" t="str">
         <f>IF(OR(Q5="",S5=""),"",IF(Indicadores!E5="Não",IF(Q5&lt;=S5,"No alvo","Acima da meta"),IF(Q5&gt;=S5,"No alvo","Abaixo da meta")))</f>
@@ -976,23 +988,23 @@
       </c>
       <c r="B6" s="9" t="str">
         <f>IF(Q6="","",IF(Indicadores!B6="R$","R$ ","")&amp;FIXED(Q6,N6)&amp;IF(Indicadores!B6="%","%",IF(OR(Indicadores!B6="R$",Indicadores!B6="",Indicadores!B6="un"),""," "&amp;Indicadores!B6)))</f>
-        <v>R$ 21,212</v>
+        <v>R$ 21.212</v>
       </c>
       <c r="C6" s="9" t="str">
         <f>IF(R6="","",IF(Indicadores!B6="R$","R$ ","")&amp;FIXED(R6,N6)&amp;IF(Indicadores!B6="%","%",IF(OR(Indicadores!B6="R$",Indicadores!B6="",Indicadores!B6="un"),""," "&amp;Indicadores!B6)))</f>
-        <v>R$ 21,167</v>
+        <v>R$ 21.167</v>
       </c>
       <c r="D6" s="9" t="str">
         <f>IF(T6="","",IF(T6&gt;=0,"+","")&amp;IF(Indicadores!B6="%",FIXED(T6,1)&amp;" p.p.",FIXED(T6*100,1)&amp;"%"))</f>
-        <v>+0.2%</v>
+        <v>+0,2%</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>IF(S6="","",IF(Indicadores!B6="R$","R$ ","")&amp;FIXED(S6,N6)&amp;IF(Indicadores!B6="%","%",IF(OR(Indicadores!B6="R$",Indicadores!B6="",Indicadores!B6="un"),""," "&amp;Indicadores!B6)))</f>
-        <v>R$ 21,500</v>
+        <v>R$ 21.500</v>
       </c>
       <c r="F6" s="9" t="str">
         <f>IF(U6="","",IF(U6&gt;=0,"+","")&amp;IF(Indicadores!B6="%",FIXED(U6,1)&amp;" p.p.",FIXED(U6*100,1)&amp;"%"))</f>
-        <v>-1.3%</v>
+        <v>-1,3%</v>
       </c>
       <c r="G6" s="9" t="str">
         <f>IF(OR(Q6="",S6=""),"",IF(Indicadores!E6="Não",IF(Q6&lt;=S6,"No alvo","Acima da meta"),IF(Q6&gt;=S6,"No alvo","Abaixo da meta")))</f>
@@ -1042,23 +1054,23 @@
       </c>
       <c r="B7" s="9" t="str">
         <f>IF(Q7="","",IF(Indicadores!B7="R$","R$ ","")&amp;FIXED(Q7,N7)&amp;IF(Indicadores!B7="%","%",IF(OR(Indicadores!B7="R$",Indicadores!B7="",Indicadores!B7="un"),""," "&amp;Indicadores!B7)))</f>
-        <v>R$ 5,688</v>
+        <v>R$ 5.688</v>
       </c>
       <c r="C7" s="9" t="str">
         <f>IF(R7="","",IF(Indicadores!B7="R$","R$ ","")&amp;FIXED(R7,N7)&amp;IF(Indicadores!B7="%","%",IF(OR(Indicadores!B7="R$",Indicadores!B7="",Indicadores!B7="un"),""," "&amp;Indicadores!B7)))</f>
-        <v>R$ 8,293</v>
+        <v>R$ 8.293</v>
       </c>
       <c r="D7" s="9" t="str">
         <f>IF(T7="","",IF(T7&gt;=0,"+","")&amp;IF(Indicadores!B7="%",FIXED(T7,1)&amp;" p.p.",FIXED(T7*100,1)&amp;"%"))</f>
-        <v>-31.4%</v>
+        <v>-31,4%</v>
       </c>
       <c r="E7" s="9" t="str">
         <f>IF(S7="","",IF(Indicadores!B7="R$","R$ ","")&amp;FIXED(S7,N7)&amp;IF(Indicadores!B7="%","%",IF(OR(Indicadores!B7="R$",Indicadores!B7="",Indicadores!B7="un"),""," "&amp;Indicadores!B7)))</f>
-        <v>R$ 4,000</v>
+        <v>R$ 4.000</v>
       </c>
       <c r="F7" s="9" t="str">
         <f>IF(U7="","",IF(U7&gt;=0,"+","")&amp;IF(Indicadores!B7="%",FIXED(U7,1)&amp;" p.p.",FIXED(U7*100,1)&amp;"%"))</f>
-        <v>+42.2%</v>
+        <v>+42,2%</v>
       </c>
       <c r="G7" s="9" t="str">
         <f>IF(OR(Q7="",S7=""),"",IF(Indicadores!E7="Não",IF(Q7&lt;=S7,"No alvo","Acima da meta"),IF(Q7&gt;=S7,"No alvo","Abaixo da meta")))</f>
@@ -1108,23 +1120,23 @@
       </c>
       <c r="B8" s="9" t="str">
         <f>IF(Q8="","",IF(Indicadores!B8="R$","R$ ","")&amp;FIXED(Q8,N8)&amp;IF(Indicadores!B8="%","%",IF(OR(Indicadores!B8="R$",Indicadores!B8="",Indicadores!B8="un"),""," "&amp;Indicadores!B8)))</f>
-        <v>21.1%</v>
+        <v>21,1%</v>
       </c>
       <c r="C8" s="9" t="str">
         <f>IF(R8="","",IF(Indicadores!B8="R$","R$ ","")&amp;FIXED(R8,N8)&amp;IF(Indicadores!B8="%","%",IF(OR(Indicadores!B8="R$",Indicadores!B8="",Indicadores!B8="un"),""," "&amp;Indicadores!B8)))</f>
-        <v>28.2%</v>
+        <v>28,2%</v>
       </c>
       <c r="D8" s="9" t="str">
         <f>IF(T8="","",IF(T8&gt;=0,"+","")&amp;IF(Indicadores!B8="%",FIXED(T8,1)&amp;" p.p.",FIXED(T8*100,1)&amp;"%"))</f>
-        <v>-7.1 p.p.</v>
+        <v>-7,1 p.p.</v>
       </c>
       <c r="E8" s="9" t="str">
         <f>IF(S8="","",IF(Indicadores!B8="R$","R$ ","")&amp;FIXED(S8,N8)&amp;IF(Indicadores!B8="%","%",IF(OR(Indicadores!B8="R$",Indicadores!B8="",Indicadores!B8="un"),""," "&amp;Indicadores!B8)))</f>
-        <v>20.0%</v>
+        <v>20,0%</v>
       </c>
       <c r="F8" s="9" t="str">
         <f>IF(U8="","",IF(U8&gt;=0,"+","")&amp;IF(Indicadores!B8="%",FIXED(U8,1)&amp;" p.p.",FIXED(U8*100,1)&amp;"%"))</f>
-        <v>+1.1 p.p.</v>
+        <v>+1,1 p.p.</v>
       </c>
       <c r="G8" s="9" t="str">
         <f>IF(OR(Q8="",S8=""),"",IF(Indicadores!E8="Não",IF(Q8&lt;=S8,"No alvo","Acima da meta"),IF(Q8&gt;=S8,"No alvo","Abaixo da meta")))</f>
@@ -1174,23 +1186,23 @@
       </c>
       <c r="B9" s="9" t="str">
         <f>IF(Q9="","",IF(Indicadores!B9="R$","R$ ","")&amp;FIXED(Q9,N9)&amp;IF(Indicadores!B9="%","%",IF(OR(Indicadores!B9="R$",Indicadores!B9="",Indicadores!B9="un"),""," "&amp;Indicadores!B9)))</f>
-        <v>304.0 h</v>
+        <v>304,0 h</v>
       </c>
       <c r="C9" s="9" t="str">
         <f>IF(R9="","",IF(Indicadores!B9="R$","R$ ","")&amp;FIXED(R9,N9)&amp;IF(Indicadores!B9="%","%",IF(OR(Indicadores!B9="R$",Indicadores!B9="",Indicadores!B9="un"),""," "&amp;Indicadores!B9)))</f>
-        <v>233.5 h</v>
+        <v>233,5 h</v>
       </c>
       <c r="D9" s="9" t="str">
         <f>IF(T9="","",IF(T9&gt;=0,"+","")&amp;IF(Indicadores!B9="%",FIXED(T9,1)&amp;" p.p.",FIXED(T9*100,1)&amp;"%"))</f>
-        <v>+30.2%</v>
+        <v>+30,2%</v>
       </c>
       <c r="E9" s="9" t="str">
         <f>IF(S9="","",IF(Indicadores!B9="R$","R$ ","")&amp;FIXED(S9,N9)&amp;IF(Indicadores!B9="%","%",IF(OR(Indicadores!B9="R$",Indicadores!B9="",Indicadores!B9="un"),""," "&amp;Indicadores!B9)))</f>
-        <v>280.0 h</v>
+        <v>280,0 h</v>
       </c>
       <c r="F9" s="9" t="str">
         <f>IF(U9="","",IF(U9&gt;=0,"+","")&amp;IF(Indicadores!B9="%",FIXED(U9,1)&amp;" p.p.",FIXED(U9*100,1)&amp;"%"))</f>
-        <v>+8.6%</v>
+        <v>+8,6%</v>
       </c>
       <c r="G9" s="9" t="str">
         <f>IF(OR(Q9="",S9=""),"",IF(Indicadores!E9="Não",IF(Q9&lt;=S9,"No alvo","Acima da meta"),IF(Q9&gt;=S9,"No alvo","Abaixo da meta")))</f>
@@ -1240,23 +1252,23 @@
       </c>
       <c r="B10" s="9" t="str">
         <f>IF(Q10="","",IF(Indicadores!B10="R$","R$ ","")&amp;FIXED(Q10,N10)&amp;IF(Indicadores!B10="%","%",IF(OR(Indicadores!B10="R$",Indicadores!B10="",Indicadores!B10="un"),""," "&amp;Indicadores!B10)))</f>
-        <v>81.6%</v>
+        <v>81,6%</v>
       </c>
       <c r="C10" s="9" t="str">
         <f>IF(R10="","",IF(Indicadores!B10="R$","R$ ","")&amp;FIXED(R10,N10)&amp;IF(Indicadores!B10="%","%",IF(OR(Indicadores!B10="R$",Indicadores!B10="",Indicadores!B10="un"),""," "&amp;Indicadores!B10)))</f>
-        <v>76.9%</v>
+        <v>76,9%</v>
       </c>
       <c r="D10" s="9" t="str">
         <f>IF(T10="","",IF(T10&gt;=0,"+","")&amp;IF(Indicadores!B10="%",FIXED(T10,1)&amp;" p.p.",FIXED(T10*100,1)&amp;"%"))</f>
-        <v>+4.7 p.p.</v>
+        <v>+4,7 p.p.</v>
       </c>
       <c r="E10" s="9" t="str">
         <f>IF(S10="","",IF(Indicadores!B10="R$","R$ ","")&amp;FIXED(S10,N10)&amp;IF(Indicadores!B10="%","%",IF(OR(Indicadores!B10="R$",Indicadores!B10="",Indicadores!B10="un"),""," "&amp;Indicadores!B10)))</f>
-        <v>75.0%</v>
+        <v>75,0%</v>
       </c>
       <c r="F10" s="9" t="str">
         <f>IF(U10="","",IF(U10&gt;=0,"+","")&amp;IF(Indicadores!B10="%",FIXED(U10,1)&amp;" p.p.",FIXED(U10*100,1)&amp;"%"))</f>
-        <v>+6.6 p.p.</v>
+        <v>+6,6 p.p.</v>
       </c>
       <c r="G10" s="9" t="str">
         <f>IF(OR(Q10="",S10=""),"",IF(Indicadores!E10="Não",IF(Q10&lt;=S10,"No alvo","Acima da meta"),IF(Q10&gt;=S10,"No alvo","Abaixo da meta")))</f>
@@ -1306,15 +1318,15 @@
       </c>
       <c r="B11" s="9" t="str">
         <f>IF(Q11="","",IF(Indicadores!B11="R$","R$ ","")&amp;FIXED(Q11,N11)&amp;IF(Indicadores!B11="%","%",IF(OR(Indicadores!B11="R$",Indicadores!B11="",Indicadores!B11="un"),""," "&amp;Indicadores!B11)))</f>
-        <v>R$ 117,210</v>
+        <v>R$ 117.210</v>
       </c>
       <c r="C11" s="9" t="str">
         <f>IF(R11="","",IF(Indicadores!B11="R$","R$ ","")&amp;FIXED(R11,N11)&amp;IF(Indicadores!B11="%","%",IF(OR(Indicadores!B11="R$",Indicadores!B11="",Indicadores!B11="un"),""," "&amp;Indicadores!B11)))</f>
-        <v>R$ 117,700</v>
+        <v>R$ 117.700</v>
       </c>
       <c r="D11" s="9" t="str">
         <f>IF(T11="","",IF(T11&gt;=0,"+","")&amp;IF(Indicadores!B11="%",FIXED(T11,1)&amp;" p.p.",FIXED(T11*100,1)&amp;"%"))</f>
-        <v>-0.4%</v>
+        <v>-0,4%</v>
       </c>
       <c r="E11" s="9">
         <f>IF(S11="","",IF(Indicadores!B11="R$","R$ ","")&amp;FIXED(S11,N11)&amp;IF(Indicadores!B11="%","%",IF(OR(Indicadores!B11="R$",Indicadores!B11="",Indicadores!B11="un"),""," "&amp;Indicadores!B11)))</f>
@@ -1372,23 +1384,23 @@
       </c>
       <c r="B12" s="9" t="str">
         <f>IF(Q12="","",IF(Indicadores!B12="R$","R$ ","")&amp;FIXED(Q12,N12)&amp;IF(Indicadores!B12="%","%",IF(OR(Indicadores!B12="R$",Indicadores!B12="",Indicadores!B12="un"),""," "&amp;Indicadores!B12)))</f>
-        <v>R$ 12,500</v>
+        <v>R$ 11.100</v>
       </c>
       <c r="C12" s="9" t="str">
         <f>IF(R12="","",IF(Indicadores!B12="R$","R$ ","")&amp;FIXED(R12,N12)&amp;IF(Indicadores!B12="%","%",IF(OR(Indicadores!B12="R$",Indicadores!B12="",Indicadores!B12="un"),""," "&amp;Indicadores!B12)))</f>
-        <v>R$ 8,900</v>
+        <v>R$ 7.500</v>
       </c>
       <c r="D12" s="9" t="str">
         <f>IF(T12="","",IF(T12&gt;=0,"+","")&amp;IF(Indicadores!B12="%",FIXED(T12,1)&amp;" p.p.",FIXED(T12*100,1)&amp;"%"))</f>
-        <v>+40.4%</v>
+        <v>+48,0%</v>
       </c>
       <c r="E12" s="9" t="str">
         <f>IF(S12="","",IF(Indicadores!B12="R$","R$ ","")&amp;FIXED(S12,N12)&amp;IF(Indicadores!B12="%","%",IF(OR(Indicadores!B12="R$",Indicadores!B12="",Indicadores!B12="un"),""," "&amp;Indicadores!B12)))</f>
-        <v>R$ 10,000</v>
+        <v>R$ 10.000</v>
       </c>
       <c r="F12" s="9" t="str">
         <f>IF(U12="","",IF(U12&gt;=0,"+","")&amp;IF(Indicadores!B12="%",FIXED(U12,1)&amp;" p.p.",FIXED(U12*100,1)&amp;"%"))</f>
-        <v>+25.0%</v>
+        <v>+11,0%</v>
       </c>
       <c r="G12" s="9" t="str">
         <f>IF(OR(Q12="",S12=""),"",IF(Indicadores!E12="Não",IF(Q12&lt;=S12,"No alvo","Acima da meta"),IF(Q12&gt;=S12,"No alvo","Abaixo da meta")))</f>
@@ -1404,19 +1416,19 @@
       </c>
       <c r="O12" s="10">
         <f>IF(OR(U12="",G12="",G12="No alvo"),"",IF(Indicadores!E12="Não",U12,-U12))</f>
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="P12" s="10">
         <f>IF(T12="","",IF(Indicadores!E12="Não",-T12,T12))</f>
-        <v>-0.404494382022472</v>
+        <v>-0.48</v>
       </c>
       <c r="Q12" s="10">
         <f>IF(OR(Indicadores!A12="",Indicadores!G12=""),"",Indicadores!G12)</f>
-        <v>12500</v>
+        <v>11100</v>
       </c>
       <c r="R12" s="10">
         <f>IF(OR(Indicadores!A12="",Indicadores!F12=""),"",Indicadores!F12)</f>
-        <v>8900</v>
+        <v>7500</v>
       </c>
       <c r="S12" s="10">
         <f>IF(OR(Indicadores!A12="",Indicadores!D12=""),"",Indicadores!D12)</f>
@@ -1424,11 +1436,11 @@
       </c>
       <c r="T12" s="10">
         <f>IF(OR(Q12="",R12=""),"",IF(Indicadores!B12="%",Q12-R12,IF(R12=0,"",(Q12-R12)/ABS(R12))))</f>
-        <v>0.404494382022472</v>
+        <v>0.48</v>
       </c>
       <c r="U12" s="10">
         <f>IF(OR(Q12="",S12=""),"",IF(Indicadores!B12="%",Q12-S12,IF(S12=0,"",(Q12-S12)/ABS(S12))))</f>
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="13">
@@ -1438,27 +1450,27 @@
       </c>
       <c r="B13" s="9" t="str">
         <f>IF(Q13="","",IF(Indicadores!B13="R$","R$ ","")&amp;FIXED(Q13,N13)&amp;IF(Indicadores!B13="%","%",IF(OR(Indicadores!B13="R$",Indicadores!B13="",Indicadores!B13="un"),""," "&amp;Indicadores!B13)))</f>
-        <v>4.5%</v>
+        <v>4,0%</v>
       </c>
       <c r="C13" s="9" t="str">
         <f>IF(R13="","",IF(Indicadores!B13="R$","R$ ","")&amp;FIXED(R13,N13)&amp;IF(Indicadores!B13="%","%",IF(OR(Indicadores!B13="R$",Indicadores!B13="",Indicadores!B13="un"),""," "&amp;Indicadores!B13)))</f>
-        <v>3.6%</v>
+        <v>3,0%</v>
       </c>
       <c r="D13" s="9" t="str">
         <f>IF(T13="","",IF(T13&gt;=0,"+","")&amp;IF(Indicadores!B13="%",FIXED(T13,1)&amp;" p.p.",FIXED(T13*100,1)&amp;"%"))</f>
-        <v>+0.9 p.p.</v>
+        <v>+1,0 p.p.</v>
       </c>
       <c r="E13" s="9" t="str">
         <f>IF(S13="","",IF(Indicadores!B13="R$","R$ ","")&amp;FIXED(S13,N13)&amp;IF(Indicadores!B13="%","%",IF(OR(Indicadores!B13="R$",Indicadores!B13="",Indicadores!B13="un"),""," "&amp;Indicadores!B13)))</f>
-        <v>4.0%</v>
+        <v>4,0%</v>
       </c>
       <c r="F13" s="9" t="str">
         <f>IF(U13="","",IF(U13&gt;=0,"+","")&amp;IF(Indicadores!B13="%",FIXED(U13,1)&amp;" p.p.",FIXED(U13*100,1)&amp;"%"))</f>
-        <v>+0.5 p.p.</v>
+        <v>+0,0 p.p.</v>
       </c>
       <c r="G13" s="9" t="str">
         <f>IF(OR(Q13="",S13=""),"",IF(Indicadores!E13="Não",IF(Q13&lt;=S13,"No alvo","Acima da meta"),IF(Q13&gt;=S13,"No alvo","Abaixo da meta")))</f>
-        <v>Acima da meta</v>
+        <v>No alvo</v>
       </c>
       <c r="H13" s="9" t="str">
         <f>IF(Indicadores!A13="","",Indicadores!B13)</f>
@@ -1470,19 +1482,19 @@
       </c>
       <c r="O13" s="10">
         <f>IF(OR(U13="",G13="",G13="No alvo"),"",IF(Indicadores!E13="Não",U13,-U13))</f>
-        <v>0.5</v>
+        <v/>
       </c>
       <c r="P13" s="10">
         <f>IF(T13="","",IF(Indicadores!E13="Não",-T13,T13))</f>
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="Q13" s="10">
         <f>IF(OR(Indicadores!A13="",Indicadores!G13=""),"",Indicadores!G13)</f>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R13" s="10">
         <f>IF(OR(Indicadores!A13="",Indicadores!F13=""),"",Indicadores!F13)</f>
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="S13" s="10">
         <f>IF(OR(Indicadores!A13="",Indicadores!D13=""),"",Indicadores!D13)</f>
@@ -1490,11 +1502,11 @@
       </c>
       <c r="T13" s="10">
         <f>IF(OR(Q13="",R13=""),"",IF(Indicadores!B13="%",Q13-R13,IF(R13=0,"",(Q13-R13)/ABS(R13))))</f>
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U13" s="10">
         <f>IF(OR(Q13="",S13=""),"",IF(Indicadores!B13="%",Q13-S13,IF(S13=0,"",(Q13-S13)/ABS(S13))))</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1504,23 +1516,23 @@
       </c>
       <c r="B14" s="9" t="str">
         <f>IF(Q14="","",IF(Indicadores!B14="R$","R$ ","")&amp;FIXED(Q14,N14)&amp;IF(Indicadores!B14="%","%",IF(OR(Indicadores!B14="R$",Indicadores!B14="",Indicadores!B14="un"),""," "&amp;Indicadores!B14)))</f>
-        <v>R$ 46,900</v>
+        <v>R$ 46.900</v>
       </c>
       <c r="C14" s="9" t="str">
         <f>IF(R14="","",IF(Indicadores!B14="R$","R$ ","")&amp;FIXED(R14,N14)&amp;IF(Indicadores!B14="%","%",IF(OR(Indicadores!B14="R$",Indicadores!B14="",Indicadores!B14="un"),""," "&amp;Indicadores!B14)))</f>
-        <v>R$ 21,600</v>
+        <v>R$ 21.600</v>
       </c>
       <c r="D14" s="9" t="str">
         <f>IF(T14="","",IF(T14&gt;=0,"+","")&amp;IF(Indicadores!B14="%",FIXED(T14,1)&amp;" p.p.",FIXED(T14*100,1)&amp;"%"))</f>
-        <v>+117.1%</v>
+        <v>+117,1%</v>
       </c>
       <c r="E14" s="9" t="str">
         <f>IF(S14="","",IF(Indicadores!B14="R$","R$ ","")&amp;FIXED(S14,N14)&amp;IF(Indicadores!B14="%","%",IF(OR(Indicadores!B14="R$",Indicadores!B14="",Indicadores!B14="un"),""," "&amp;Indicadores!B14)))</f>
-        <v>R$ 40,000</v>
+        <v>R$ 40.000</v>
       </c>
       <c r="F14" s="9" t="str">
         <f>IF(U14="","",IF(U14&gt;=0,"+","")&amp;IF(Indicadores!B14="%",FIXED(U14,1)&amp;" p.p.",FIXED(U14*100,1)&amp;"%"))</f>
-        <v>+17.3%</v>
+        <v>+17,3%</v>
       </c>
       <c r="G14" s="9" t="str">
         <f>IF(OR(Q14="",S14=""),"",IF(Indicadores!E14="Não",IF(Q14&lt;=S14,"No alvo","Acima da meta"),IF(Q14&gt;=S14,"No alvo","Abaixo da meta")))</f>
@@ -1578,7 +1590,7 @@
       </c>
       <c r="D15" s="9" t="str">
         <f>IF(T15="","",IF(T15&gt;=0,"+","")&amp;IF(Indicadores!B15="%",FIXED(T15,1)&amp;" p.p.",FIXED(T15*100,1)&amp;"%"))</f>
-        <v>+7.1%</v>
+        <v>+7,1%</v>
       </c>
       <c r="E15" s="9" t="str">
         <f>IF(S15="","",IF(Indicadores!B15="R$","R$ ","")&amp;FIXED(S15,N15)&amp;IF(Indicadores!B15="%","%",IF(OR(Indicadores!B15="R$",Indicadores!B15="",Indicadores!B15="un"),""," "&amp;Indicadores!B15)))</f>
@@ -1586,7 +1598,7 @@
       </c>
       <c r="F15" s="9" t="str">
         <f>IF(U15="","",IF(U15&gt;=0,"+","")&amp;IF(Indicadores!B15="%",FIXED(U15,1)&amp;" p.p.",FIXED(U15*100,1)&amp;"%"))</f>
-        <v>+0.0%</v>
+        <v>+0,0%</v>
       </c>
       <c r="G15" s="9" t="str">
         <f>IF(OR(Q15="",S15=""),"",IF(Indicadores!E15="Não",IF(Q15&lt;=S15,"No alvo","Acima da meta"),IF(Q15&gt;=S15,"No alvo","Abaixo da meta")))</f>
@@ -1636,23 +1648,23 @@
       </c>
       <c r="B16" s="9" t="str">
         <f>IF(Q16="","",IF(Indicadores!B16="R$","R$ ","")&amp;FIXED(Q16,N16)&amp;IF(Indicadores!B16="%","%",IF(OR(Indicadores!B16="R$",Indicadores!B16="",Indicadores!B16="un"),""," "&amp;Indicadores!B16)))</f>
-        <v>R$ 26,100</v>
+        <v>R$ 26.100</v>
       </c>
       <c r="C16" s="9" t="str">
         <f>IF(R16="","",IF(Indicadores!B16="R$","R$ ","")&amp;FIXED(R16,N16)&amp;IF(Indicadores!B16="%","%",IF(OR(Indicadores!B16="R$",Indicadores!B16="",Indicadores!B16="un"),""," "&amp;Indicadores!B16)))</f>
-        <v>R$ 26,900</v>
+        <v>R$ 26.900</v>
       </c>
       <c r="D16" s="9" t="str">
         <f>IF(T16="","",IF(T16&gt;=0,"+","")&amp;IF(Indicadores!B16="%",FIXED(T16,1)&amp;" p.p.",FIXED(T16*100,1)&amp;"%"))</f>
-        <v>-3.0%</v>
+        <v>-3,0%</v>
       </c>
       <c r="E16" s="9" t="str">
         <f>IF(S16="","",IF(Indicadores!B16="R$","R$ ","")&amp;FIXED(S16,N16)&amp;IF(Indicadores!B16="%","%",IF(OR(Indicadores!B16="R$",Indicadores!B16="",Indicadores!B16="un"),""," "&amp;Indicadores!B16)))</f>
-        <v>R$ 20,000</v>
+        <v>R$ 20.000</v>
       </c>
       <c r="F16" s="9" t="str">
         <f>IF(U16="","",IF(U16&gt;=0,"+","")&amp;IF(Indicadores!B16="%",FIXED(U16,1)&amp;" p.p.",FIXED(U16*100,1)&amp;"%"))</f>
-        <v>+30.5%</v>
+        <v>+30,5%</v>
       </c>
       <c r="G16" s="9" t="str">
         <f>IF(OR(Q16="",S16=""),"",IF(Indicadores!E16="Não",IF(Q16&lt;=S16,"No alvo","Acima da meta"),IF(Q16&gt;=S16,"No alvo","Abaixo da meta")))</f>
@@ -1766,7 +1778,7 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>Agosto fechou com quatro propostas novas viradas em caso (Escola Aurora, Loja Verde, Marcos Vinícius e a cobrança da Construtora entrou em julho); Bistrô 42 e Agência Prisma seguem com parcelas vencidas e entraram na régua de cobrança; o caso da Oficina (execução) e o recurso da Escola Aurora estouraram as horas estimadas.</t>
+          <t>Agosto fechou com três propostas novas viradas em caso (Escola Aurora, Loja Verde e Marcos Vinícius); a cobrança da Construtora já havia entrado em julho e não conta neste mês; Bistrô 42 e Agência Prisma seguem com parcelas vencidas e entraram na régua de cobrança; o caso da Oficina (execução) e o recurso da Escola Aurora estouraram as horas estimadas.</t>
         </is>
       </c>
       <c r="B6" s="15" t="n"/>
@@ -1775,74 +1787,74 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="str">
-        <f>IF(OR(Painel!A5="",Painel!Q5=""),"","• "&amp;Painel!A5&amp;": "&amp;Painel!B5&amp;IF(Painel!T5&lt;&gt;"",IF(Painel!T5=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D5&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(Painel!R5&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")",""))&amp;IF(Painel!S5&lt;&gt;"","; meta "&amp;Painel!E5&amp;", "&amp;LOWER(Painel!G5),"")&amp;".")</f>
-        <v>• Entrou no mês (recebimentos): R$ 26,900 (-8.7% em relação a Julho); meta R$ 26,000, no alvo.</v>
+        <f>IF(OR(Painel!A5="",Painel!Q5=""),"","• "&amp;Painel!A5&amp;": "&amp;Painel!B5&amp;IF(Painel!T5&lt;&gt;"",IF(Painel!T5=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D5&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(AND(Painel!R5&lt;&gt;"",Painel!R5=0,Painel!Q5&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!R5&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")","")))&amp;IF(Painel!S5&lt;&gt;"","; meta "&amp;Painel!E5&amp;", "&amp;LOWER(Painel!G5),"")&amp;".")</f>
+        <v>• Entrou no mês (recebimentos): R$ 26.900 (-8,7% em relação a Julho); meta R$ 26.000, no alvo.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="str">
-        <f>IF(OR(Painel!A6="",Painel!Q6=""),"","• "&amp;Painel!A6&amp;": "&amp;Painel!B6&amp;IF(Painel!T6&lt;&gt;"",IF(Painel!T6=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D6&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(Painel!R6&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")",""))&amp;IF(Painel!S6&lt;&gt;"","; meta "&amp;Painel!E6&amp;", "&amp;LOWER(Painel!G6),"")&amp;".")</f>
-        <v>• Saídas do mês (custos, despesas de casos, pró-labore e impostos provisionados): R$ 21,212 (+0.2% em relação a Julho); meta R$ 21,500, no alvo.</v>
+        <f>IF(OR(Painel!A6="",Painel!Q6=""),"","• "&amp;Painel!A6&amp;": "&amp;Painel!B6&amp;IF(Painel!T6&lt;&gt;"",IF(Painel!T6=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D6&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(AND(Painel!R6&lt;&gt;"",Painel!R6=0,Painel!Q6&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!R6&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")","")))&amp;IF(Painel!S6&lt;&gt;"","; meta "&amp;Painel!E6&amp;", "&amp;LOWER(Painel!G6),"")&amp;".")</f>
+        <v>• Saídas do mês (custos, despesas de casos, pró-labore e impostos provisionados): R$ 21.212 (+0,2% em relação a Julho); meta R$ 21.500, no alvo.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="str">
-        <f>IF(OR(Painel!A7="",Painel!Q7=""),"","• "&amp;Painel!A7&amp;": "&amp;Painel!B7&amp;IF(Painel!T7&lt;&gt;"",IF(Painel!T7=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D7&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(Painel!R7&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")",""))&amp;IF(Painel!S7&lt;&gt;"","; meta "&amp;Painel!E7&amp;", "&amp;LOWER(Painel!G7),"")&amp;".")</f>
-        <v>• Resultado do mês: R$ 5,688 (-31.4% em relação a Julho); meta R$ 4,000, no alvo.</v>
+        <f>IF(OR(Painel!A7="",Painel!Q7=""),"","• "&amp;Painel!A7&amp;": "&amp;Painel!B7&amp;IF(Painel!T7&lt;&gt;"",IF(Painel!T7=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D7&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(AND(Painel!R7&lt;&gt;"",Painel!R7=0,Painel!Q7&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!R7&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")","")))&amp;IF(Painel!S7&lt;&gt;"","; meta "&amp;Painel!E7&amp;", "&amp;LOWER(Painel!G7),"")&amp;".")</f>
+        <v>• Resultado do mês: R$ 5.688 (-31,4% em relação a Julho); meta R$ 4.000, no alvo.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="str">
-        <f>IF(OR(Painel!A8="",Painel!Q8=""),"","• "&amp;Painel!A8&amp;": "&amp;Painel!B8&amp;IF(Painel!T8&lt;&gt;"",IF(Painel!T8=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D8&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(Painel!R8&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")",""))&amp;IF(Painel!S8&lt;&gt;"","; meta "&amp;Painel!E8&amp;", "&amp;LOWER(Painel!G8),"")&amp;".")</f>
-        <v>• Margem do mês: 21.1% (-7.1 p.p. em relação a Julho); meta 20.0%, no alvo.</v>
+        <f>IF(OR(Painel!A8="",Painel!Q8=""),"","• "&amp;Painel!A8&amp;": "&amp;Painel!B8&amp;IF(Painel!T8&lt;&gt;"",IF(Painel!T8=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D8&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(AND(Painel!R8&lt;&gt;"",Painel!R8=0,Painel!Q8&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!R8&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")","")))&amp;IF(Painel!S8&lt;&gt;"","; meta "&amp;Painel!E8&amp;", "&amp;LOWER(Painel!G8),"")&amp;".")</f>
+        <v>• Margem do mês: 21,1% (-7,1 p.p. em relação a Julho); meta 20,0%, no alvo.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="str">
-        <f>IF(OR(Painel!A9="",Painel!Q9=""),"","• "&amp;Painel!A9&amp;": "&amp;Painel!B9&amp;IF(Painel!T9&lt;&gt;"",IF(Painel!T9=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D9&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(Painel!R9&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")",""))&amp;IF(Painel!S9&lt;&gt;"","; meta "&amp;Painel!E9&amp;", "&amp;LOWER(Painel!G9),"")&amp;".")</f>
-        <v>• Horas registradas no mês: 304.0 h (+30.2% em relação a Julho); meta 280.0 h, no alvo.</v>
+        <f>IF(OR(Painel!A9="",Painel!Q9=""),"","• "&amp;Painel!A9&amp;": "&amp;Painel!B9&amp;IF(Painel!T9&lt;&gt;"",IF(Painel!T9=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D9&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(AND(Painel!R9&lt;&gt;"",Painel!R9=0,Painel!Q9&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!R9&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")","")))&amp;IF(Painel!S9&lt;&gt;"","; meta "&amp;Painel!E9&amp;", "&amp;LOWER(Painel!G9),"")&amp;".")</f>
+        <v>• Horas registradas no mês: 304,0 h (+30,2% em relação a Julho); meta 280,0 h, no alvo.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="str">
-        <f>IF(OR(Painel!A10="",Painel!Q10=""),"","• "&amp;Painel!A10&amp;": "&amp;Painel!B10&amp;IF(Painel!T10&lt;&gt;"",IF(Painel!T10=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D10&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(Painel!R10&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")",""))&amp;IF(Painel!S10&lt;&gt;"","; meta "&amp;Painel!E10&amp;", "&amp;LOWER(Painel!G10),"")&amp;".")</f>
-        <v>• Horas faturáveis: 81.6% (+4.7 p.p. em relação a Julho); meta 75.0%, no alvo.</v>
+        <f>IF(OR(Painel!A10="",Painel!Q10=""),"","• "&amp;Painel!A10&amp;": "&amp;Painel!B10&amp;IF(Painel!T10&lt;&gt;"",IF(Painel!T10=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D10&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(AND(Painel!R10&lt;&gt;"",Painel!R10=0,Painel!Q10&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!R10&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")","")))&amp;IF(Painel!S10&lt;&gt;"","; meta "&amp;Painel!E10&amp;", "&amp;LOWER(Painel!G10),"")&amp;".")</f>
+        <v>• Horas faturáveis: 81,6% (+4,7 p.p. em relação a Julho); meta 75,0%, no alvo.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="str">
-        <f>IF(OR(Painel!A11="",Painel!Q11=""),"","• "&amp;Painel!A11&amp;": "&amp;Painel!B11&amp;IF(Painel!T11&lt;&gt;"",IF(Painel!T11=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D11&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(Painel!R11&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")",""))&amp;IF(Painel!S11&lt;&gt;"","; meta "&amp;Painel!E11&amp;", "&amp;LOWER(Painel!G11),"")&amp;".")</f>
-        <v>• A receber (carteira; inclui êxito de casos ativos): R$ 117,210 (-0.4% em relação a Julho).</v>
+        <f>IF(OR(Painel!A11="",Painel!Q11=""),"","• "&amp;Painel!A11&amp;": "&amp;Painel!B11&amp;IF(Painel!T11&lt;&gt;"",IF(Painel!T11=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D11&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(AND(Painel!R11&lt;&gt;"",Painel!R11=0,Painel!Q11&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!R11&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")","")))&amp;IF(Painel!S11&lt;&gt;"","; meta "&amp;Painel!E11&amp;", "&amp;LOWER(Painel!G11),"")&amp;".")</f>
+        <v>• A receber (carteira; inclui êxito de casos ativos): R$ 117.210 (-0,4% em relação a Julho).</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="str">
-        <f>IF(OR(Painel!A12="",Painel!Q12=""),"","• "&amp;Painel!A12&amp;": "&amp;Painel!B12&amp;IF(Painel!T12&lt;&gt;"",IF(Painel!T12=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D12&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(Painel!R12&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")",""))&amp;IF(Painel!S12&lt;&gt;"","; meta "&amp;Painel!E12&amp;", "&amp;LOWER(Painel!G12),"")&amp;".")</f>
-        <v>• Vencido (parcelas em atraso): R$ 12,500 (+40.4% em relação a Julho); meta R$ 10,000, acima da meta.</v>
+        <f>IF(OR(Painel!A12="",Painel!Q12=""),"","• "&amp;Painel!A12&amp;": "&amp;Painel!B12&amp;IF(Painel!T12&lt;&gt;"",IF(Painel!T12=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D12&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(AND(Painel!R12&lt;&gt;"",Painel!R12=0,Painel!Q12&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!R12&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")","")))&amp;IF(Painel!S12&lt;&gt;"","; meta "&amp;Painel!E12&amp;", "&amp;LOWER(Painel!G12),"")&amp;".")</f>
+        <v>• Vencido (parcelas em atraso): R$ 11.100 (+48,0% em relação a Julho); meta R$ 10.000, acima da meta.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="str">
-        <f>IF(OR(Painel!A13="",Painel!Q13=""),"","• "&amp;Painel!A13&amp;": "&amp;Painel!B13&amp;IF(Painel!T13&lt;&gt;"",IF(Painel!T13=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D13&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(Painel!R13&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")",""))&amp;IF(Painel!S13&lt;&gt;"","; meta "&amp;Painel!E13&amp;", "&amp;LOWER(Painel!G13),"")&amp;".")</f>
-        <v>• Inadimplência (vencido ÷ (pago + vencido)): 4.5% (+0.9 p.p. em relação a Julho); meta 4.0%, acima da meta.</v>
+        <f>IF(OR(Painel!A13="",Painel!Q13=""),"","• "&amp;Painel!A13&amp;": "&amp;Painel!B13&amp;IF(Painel!T13&lt;&gt;"",IF(Painel!T13=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D13&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(AND(Painel!R13&lt;&gt;"",Painel!R13=0,Painel!Q13&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!R13&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")","")))&amp;IF(Painel!S13&lt;&gt;"","; meta "&amp;Painel!E13&amp;", "&amp;LOWER(Painel!G13),"")&amp;".")</f>
+        <v>• Inadimplência (vencido ÷ (pago + vencido)): 4,0% (+1,0 p.p. em relação a Julho); meta 4,0%, no alvo.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="str">
-        <f>IF(OR(Painel!A14="",Painel!Q14=""),"","• "&amp;Painel!A14&amp;": "&amp;Painel!B14&amp;IF(Painel!T14&lt;&gt;"",IF(Painel!T14=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D14&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(Painel!R14&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")",""))&amp;IF(Painel!S14&lt;&gt;"","; meta "&amp;Painel!E14&amp;", "&amp;LOWER(Painel!G14),"")&amp;".")</f>
-        <v>• Propostas abertas (valor): R$ 46,900 (+117.1% em relação a Julho); meta R$ 40,000, no alvo.</v>
+        <f>IF(OR(Painel!A14="",Painel!Q14=""),"","• "&amp;Painel!A14&amp;": "&amp;Painel!B14&amp;IF(Painel!T14&lt;&gt;"",IF(Painel!T14=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D14&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(AND(Painel!R14&lt;&gt;"",Painel!R14=0,Painel!Q14&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!R14&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")","")))&amp;IF(Painel!S14&lt;&gt;"","; meta "&amp;Painel!E14&amp;", "&amp;LOWER(Painel!G14),"")&amp;".")</f>
+        <v>• Propostas abertas (valor): R$ 46.900 (+117,1% em relação a Julho); meta R$ 40.000, no alvo.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="str">
-        <f>IF(OR(Painel!A15="",Painel!Q15=""),"","• "&amp;Painel!A15&amp;": "&amp;Painel!B15&amp;IF(Painel!T15&lt;&gt;"",IF(Painel!T15=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D15&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(Painel!R15&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")",""))&amp;IF(Painel!S15&lt;&gt;"","; meta "&amp;Painel!E15&amp;", "&amp;LOWER(Painel!G15),"")&amp;".")</f>
-        <v>• Casos ativos: 30 (+7.1% em relação a Julho); meta 30, no alvo.</v>
+        <f>IF(OR(Painel!A15="",Painel!Q15=""),"","• "&amp;Painel!A15&amp;": "&amp;Painel!B15&amp;IF(Painel!T15&lt;&gt;"",IF(Painel!T15=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D15&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(AND(Painel!R15&lt;&gt;"",Painel!R15=0,Painel!Q15&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!R15&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")","")))&amp;IF(Painel!S15&lt;&gt;"","; meta "&amp;Painel!E15&amp;", "&amp;LOWER(Painel!G15),"")&amp;".")</f>
+        <v>• Casos ativos: 30 (+7,1% em relação a Julho); meta 30, no alvo.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="str">
-        <f>IF(OR(Painel!A16="",Painel!Q16=""),"","• "&amp;Painel!A16&amp;": "&amp;Painel!B16&amp;IF(Painel!T16&lt;&gt;"",IF(Painel!T16=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D16&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(Painel!R16&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")",""))&amp;IF(Painel!S16&lt;&gt;"","; meta "&amp;Painel!E16&amp;", "&amp;LOWER(Painel!G16),"")&amp;".")</f>
-        <v>• Honorários fechados em propostas no mês: R$ 26,100 (-3.0% em relação a Julho); meta R$ 20,000, no alvo.</v>
+        <f>IF(OR(Painel!A16="",Painel!Q16=""),"","• "&amp;Painel!A16&amp;": "&amp;Painel!B16&amp;IF(Painel!T16&lt;&gt;"",IF(Painel!T16=0," (igual a "&amp;Config!$B$8&amp;")"," ("&amp;Painel!D16&amp;" em relação a "&amp;Config!$B$8&amp;")"),IF(AND(Painel!R16&lt;&gt;"",Painel!R16=0,Painel!Q16&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!R16&lt;&gt;""," (igual a "&amp;Config!$B$8&amp;")","")))&amp;IF(Painel!S16&lt;&gt;"","; meta "&amp;Painel!E16&amp;", "&amp;LOWER(Painel!G16),"")&amp;".")</f>
+        <v>• Honorários fechados em propostas no mês: R$ 26.100 (-3,0% em relação a Julho); meta R$ 20.000, no alvo.</v>
       </c>
     </row>
     <row r="21">
@@ -1855,25 +1867,25 @@
     <row r="22">
       <c r="A22" s="17" t="str">
         <f>IF(COUNT(Painel!$P$5:$P$16)=0,"• Melhora e piora: preencha o mês anterior para comparar.",IF(MAX(Painel!$P$5:$P$16)&lt;=0,"• Nenhum indicador melhorou contra "&amp;Config!$B$8&amp;".","• Maior melhora contra "&amp;Config!$B$8&amp;": "&amp;INDEX(Painel!$A$5:$A$16,MATCH(MAX(Painel!$P$5:$P$16),Painel!$P$5:$P$16,0))&amp;" ("&amp;INDEX(Painel!$D$5:$D$16,MATCH(MAX(Painel!$P$5:$P$16),Painel!$P$5:$P$16,0))&amp;")."))</f>
-        <v>• Maior melhora contra Julho: Horas faturáveis (+4.7 p.p.).</v>
+        <v>• Maior melhora contra Julho: Horas faturáveis (+4,7 p.p.).</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="str">
         <f>IF(COUNT(Painel!$P$5:$P$16)=0,"",IF(MIN(Painel!$P$5:$P$16)&gt;=0,"• Nenhum indicador piorou contra "&amp;Config!$B$8&amp;".","• Maior piora contra "&amp;Config!$B$8&amp;": "&amp;INDEX(Painel!$A$5:$A$16,MATCH(MIN(Painel!$P$5:$P$16),Painel!$P$5:$P$16,0))&amp;" ("&amp;INDEX(Painel!$D$5:$D$16,MATCH(MIN(Painel!$P$5:$P$16),Painel!$P$5:$P$16,0))&amp;")."))</f>
-        <v>• Maior piora contra Julho: Margem do mês (-7.1 p.p.).</v>
+        <v>• Maior piora contra Julho: Margem do mês (-7,1 p.p.).</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="str">
-        <f>IF(COUNT(Painel!$O$5:$O$16)=0,"• Nenhum indicador fora da meta.","• Mais longe da meta: "&amp;INDEX(Painel!$A$5:$A$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))&amp;" ("&amp;INDEX(Painel!$F$5:$F$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))&amp;" da meta, "&amp;LOWER(INDEX(Painel!$G$5:$G$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0)))&amp;").")</f>
-        <v>• Mais longe da meta: Inadimplência (vencido ÷ (pago + vencido)) (+0.5 p.p. da meta, acima da meta).</v>
+        <f>IF((COUNTIF(Painel!$G$5:$G$16,"Acima da meta")+COUNTIF(Painel!$G$5:$G$16,"Abaixo da meta"))=0,"• Nenhum indicador fora da meta.",IF(COUNT(Painel!$O$5:$O$16)=0,"• "&amp;(COUNTIF(Painel!$G$5:$G$16,"Acima da meta")+COUNTIF(Painel!$G$5:$G$16,"Abaixo da meta"))&amp;" indicador(es) fora da meta (sem percentual: a meta é zero).","• Mais longe da meta: "&amp;INDEX(Painel!$A$5:$A$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))&amp;" ("&amp;INDEX(Painel!$F$5:$F$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))&amp;" da meta, "&amp;LOWER(INDEX(Painel!$G$5:$G$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0)))&amp;")."))</f>
+        <v>• Mais longe da meta: Vencido (parcelas em atraso) (+11,0% da meta, acima da meta).</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="str">
         <f>"• Indicadores no alvo: "&amp;COUNTIF(Painel!$G$5:$G$16,"No alvo")&amp;" de "&amp;(COUNTIF(Painel!$G$5:$G$16,"No alvo")+COUNTIF(Painel!$G$5:$G$16,"Acima da meta")+COUNTIF(Painel!$G$5:$G$16,"Abaixo da meta"))&amp;" com meta."</f>
-        <v>• Indicadores no alvo: 9 de 11 com meta.</v>
+        <v>• Indicadores no alvo: 10 de 11 com meta.</v>
       </c>
     </row>
     <row r="27">
@@ -1888,24 +1900,24 @@
         <f>A4&amp;CHAR(10)&amp;CHAR(10)&amp;"Indicadores do mês:"&amp;CHAR(10)&amp;IF(A8="","",A8&amp;CHAR(10)) &amp; IF(A9="","",A9&amp;CHAR(10)) &amp; IF(A10="","",A10&amp;CHAR(10)) &amp; IF(A11="","",A11&amp;CHAR(10)) &amp; IF(A12="","",A12&amp;CHAR(10)) &amp; IF(A13="","",A13&amp;CHAR(10)) &amp; IF(A14="","",A14&amp;CHAR(10)) &amp; IF(A15="","",A15&amp;CHAR(10)) &amp; IF(A16="","",A16&amp;CHAR(10)) &amp; IF(A17="","",A17&amp;CHAR(10)) &amp; IF(A18="","",A18&amp;CHAR(10)) &amp; IF(A19="","",A19&amp;CHAR(10))&amp;CHAR(10)&amp;"Destaques:"&amp;CHAR(10)&amp;IF(A22="","",A22&amp;CHAR(10)) &amp; IF(A23="","",A23&amp;CHAR(10)) &amp; IF(A24="","",A24&amp;CHAR(10)) &amp; IF(A25="","",A25&amp;CHAR(10))&amp;IF(A6="","",CHAR(10)&amp;"Observações do escritório: "&amp;A6)</f>
         <v>Resumo de Agosto de 2026 · Ferraz &amp; Lima Advocacia (exemplo fictício)
 Indicadores do mês:
-• Entrou no mês (recebimentos): R$ 26,900 (-8.7% em relação a Julho); meta R$ 26,000, no alvo.
-• Saídas do mês (custos, despesas de casos, pró-labore e impostos provisionados): R$ 21,212 (+0.2% em relação a Julho); meta R$ 21,500, no alvo.
-• Resultado do mês: R$ 5,688 (-31.4% em relação a Julho); meta R$ 4,000, no alvo.
-• Margem do mês: 21.1% (-7.1 p.p. em relação a Julho); meta 20.0%, no alvo.
-• Horas registradas no mês: 304.0 h (+30.2% em relação a Julho); meta 280.0 h, no alvo.
-• Horas faturáveis: 81.6% (+4.7 p.p. em relação a Julho); meta 75.0%, no alvo.
-• A receber (carteira; inclui êxito de casos ativos): R$ 117,210 (-0.4% em relação a Julho).
-• Vencido (parcelas em atraso): R$ 12,500 (+40.4% em relação a Julho); meta R$ 10,000, acima da meta.
-• Inadimplência (vencido ÷ (pago + vencido)): 4.5% (+0.9 p.p. em relação a Julho); meta 4.0%, acima da meta.
-• Propostas abertas (valor): R$ 46,900 (+117.1% em relação a Julho); meta R$ 40,000, no alvo.
-• Casos ativos: 30 (+7.1% em relação a Julho); meta 30, no alvo.
-• Honorários fechados em propostas no mês: R$ 26,100 (-3.0% em relação a Julho); meta R$ 20,000, no alvo.
+• Entrou no mês (recebimentos): R$ 26.900 (-8,7% em relação a Julho); meta R$ 26.000, no alvo.
+• Saídas do mês (custos, despesas de casos, pró-labore e impostos provisionados): R$ 21.212 (+0,2% em relação a Julho); meta R$ 21.500, no alvo.
+• Resultado do mês: R$ 5.688 (-31,4% em relação a Julho); meta R$ 4.000, no alvo.
+• Margem do mês: 21,1% (-7,1 p.p. em relação a Julho); meta 20,0%, no alvo.
+• Horas registradas no mês: 304,0 h (+30,2% em relação a Julho); meta 280,0 h, no alvo.
+• Horas faturáveis: 81,6% (+4,7 p.p. em relação a Julho); meta 75,0%, no alvo.
+• A receber (carteira; inclui êxito de casos ativos): R$ 117.210 (-0,4% em relação a Julho).
+• Vencido (parcelas em atraso): R$ 11.100 (+48,0% em relação a Julho); meta R$ 10.000, acima da meta.
+• Inadimplência (vencido ÷ (pago + vencido)): 4,0% (+1,0 p.p. em relação a Julho); meta 4,0%, no alvo.
+• Propostas abertas (valor): R$ 46.900 (+117,1% em relação a Julho); meta R$ 40.000, no alvo.
+• Casos ativos: 30 (+7,1% em relação a Julho); meta 30, no alvo.
+• Honorários fechados em propostas no mês: R$ 26.100 (-3,0% em relação a Julho); meta R$ 20.000, no alvo.
 Destaques:
-• Maior melhora contra Julho: Horas faturáveis (+4.7 p.p.).
-• Maior piora contra Julho: Margem do mês (-7.1 p.p.).
-• Mais longe da meta: Inadimplência (vencido ÷ (pago + vencido)) (+0.5 p.p. da meta, acima da meta).
-• Indicadores no alvo: 9 de 11 com meta.
-Observações do escritório: Agosto fechou com quatro propostas novas viradas em caso (Escola Aurora, Loja Verde, Marcos Vinícius e a cobrança da Construtora entrou em julho); Bistrô 42 e Agência Prisma seguem com parcelas vencidas e entraram na régua de cobrança; o caso da Oficina (execução) e o recurso da Escola Aurora estouraram as horas estimadas.</v>
+• Maior melhora contra Julho: Horas faturáveis (+4,7 p.p.).
+• Maior piora contra Julho: Margem do mês (-7,1 p.p.).
+• Mais longe da meta: Vencido (parcelas em atraso) (+11,0% da meta, acima da meta).
+• Indicadores no alvo: 10 de 11 com meta.
+Observações do escritório: Agosto fechou com três propostas novas viradas em caso (Escola Aurora, Loja Verde e Marcos Vinícius); a cobrança da Construtora já havia entrado em julho e não conta neste mês; Bistrô 42 e Agência Prisma seguem com parcelas vencidas e entraram na régua de cobrança; o caso da Oficina (execução) e o recurso da Escola Aurora estouraram as horas estimadas.</v>
       </c>
     </row>
     <row r="30">
@@ -2464,10 +2476,10 @@
         </is>
       </c>
       <c r="F12" s="26" t="n">
-        <v>8900</v>
+        <v>7500</v>
       </c>
       <c r="G12" s="26" t="n">
-        <v>12500</v>
+        <v>11100</v>
       </c>
       <c r="H12" s="27" t="inlineStr">
         <is>
@@ -2498,10 +2510,10 @@
         </is>
       </c>
       <c r="F13" s="26" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G13" s="26" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H13" s="27" t="inlineStr">
         <is>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/20-resumo-do-mes.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/20-resumo-do-mes.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/20-resumo-do-mes.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/20-resumo-do-mes.xlsx
@@ -659,6 +659,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -787,7 +788,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e semáforos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
